--- a/hall/resources/sample/MGLuckyTreasure.xlsx
+++ b/hall/resources/sample/MGLuckyTreasure.xlsx
@@ -50,7 +50,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1. 实物
+1. 其它
 2. 道具</t>
         </r>
       </text>
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>序列ID</t>
   </si>
@@ -115,6 +115,9 @@
     <t>商品ID</t>
   </si>
   <si>
+    <t>商品名称</t>
+  </si>
+  <si>
     <t>商品数量</t>
   </si>
   <si>
@@ -124,28 +127,31 @@
     <t>总份数</t>
   </si>
   <si>
-    <t>单份需要道具数(ID_NUM)</t>
+    <t>单份道具数</t>
   </si>
   <si>
     <t>每局抢购时间(分钟)</t>
   </si>
   <si>
-    <t>图片资源</t>
-  </si>
-  <si>
-    <t>商品名称</t>
-  </si>
-  <si>
     <t>领奖时间(分)</t>
   </si>
   <si>
+    <t>商品图片资源</t>
+  </si>
+  <si>
+    <t>开启状态</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>string</t>
+    <t>bool</t>
   </si>
   <si>
     <t>id</t>
@@ -154,31 +160,37 @@
     <t>type</t>
   </si>
   <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>ItemNum</t>
-  </si>
-  <si>
-    <t>BestValue</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Consumption</t>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>itemNum</t>
+  </si>
+  <si>
+    <t>bestValue</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>consumption</t>
   </si>
   <si>
     <t>time</t>
   </si>
   <si>
-    <t>Des</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>collectime</t>
+    <t>collecTime</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>isOpen</t>
+  </si>
+  <si>
+    <t>Audi</t>
   </si>
   <si>
     <t>1022503_1</t>
@@ -187,13 +199,10 @@
     <t>wdcc_ccb_3.png</t>
   </si>
   <si>
-    <t>Audi</t>
+    <t>Honda</t>
   </si>
   <si>
     <t>itemicon_1010201.png</t>
-  </si>
-  <si>
-    <t>Honda</t>
   </si>
 </sst>
 </file>
@@ -376,12 +385,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1204,22 +1213,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="7" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="3" customWidth="1"/>
-    <col min="4" max="5" width="9.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7" style="3" customWidth="1"/>
-    <col min="7" max="7" width="24.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="26.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="4" max="4" width="12" style="3" customWidth="1"/>
+    <col min="5" max="6" width="9.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="7" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1229,7 +1239,7 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1241,7 +1251,7 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -1253,91 +1263,101 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>11</v>
+      <c r="L2" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="I3" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:11">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1345,32 +1365,35 @@
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>10000</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="H5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1">
         <v>4320</v>
       </c>
+      <c r="K5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:11">
+    <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1378,32 +1401,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>12000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="H6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="1">
         <v>5</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="J6" s="1">
         <v>4320</v>
       </c>
+      <c r="K6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:11">
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1413,26 +1439,29 @@
       <c r="C7" s="2">
         <v>1023001</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>50</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>14000</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>200</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="1">
-        <v>8</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="H7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1">
         <v>4320</v>
       </c>
+      <c r="L7" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1442,26 +1471,29 @@
       <c r="C8" s="2">
         <v>1023101</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>100</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>16000</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>200</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="H8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1">
         <v>10</v>
       </c>
-      <c r="K8" s="1">
+      <c r="J8" s="1">
         <v>4320</v>
       </c>
+      <c r="L8" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
+    <row r="9" s="2" customFormat="1" spans="1:12">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -1471,26 +1503,29 @@
       <c r="C9" s="2">
         <v>1023201</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>100</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>18000</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>300</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1">
-        <v>12</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="H9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1">
+        <v>10</v>
+      </c>
+      <c r="J9" s="1">
         <v>4320</v>
       </c>
+      <c r="L9" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
+    <row r="10" s="2" customFormat="1" spans="1:12">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -1500,26 +1535,29 @@
       <c r="C10" s="2">
         <v>1023301</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>100</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>20000</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>300</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="1">
-        <v>14</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="H10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1">
         <v>4320</v>
       </c>
+      <c r="L10" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:11">
+    <row r="11" s="2" customFormat="1" spans="1:12">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -1529,26 +1567,29 @@
       <c r="C11" s="2">
         <v>1023203</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>50</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>22000</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>400</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="1">
-        <v>16</v>
-      </c>
-      <c r="K11" s="1">
+      <c r="H11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="1">
+        <v>20</v>
+      </c>
+      <c r="J11" s="1">
         <v>4320</v>
       </c>
+      <c r="L11" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:11">
+    <row r="12" s="2" customFormat="1" spans="1:12">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -1558,26 +1599,29 @@
       <c r="C12" s="2">
         <v>1023303</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>50</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>24000</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>400</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="1">
-        <v>18</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="H12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="1">
+        <v>20</v>
+      </c>
+      <c r="J12" s="1">
         <v>4320</v>
       </c>
+      <c r="L12" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:11">
+    <row r="13" s="2" customFormat="1" spans="1:12">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -1587,23 +1631,26 @@
       <c r="C13" s="2">
         <v>1023403</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>50</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>26000</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>500</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="H13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1">
         <v>20</v>
       </c>
-      <c r="K13" s="1">
+      <c r="J13" s="1">
         <v>4320</v>
+      </c>
+      <c r="L13" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1"/>

--- a/hall/resources/sample/MGLuckyTreasure.xlsx
+++ b/hall/resources/sample/MGLuckyTreasure.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="41">
   <si>
     <t>序列ID</t>
   </si>
@@ -142,6 +142,15 @@
     <t>开启状态</t>
   </si>
   <si>
+    <t>机器人购买上限万分比</t>
+  </si>
+  <si>
+    <t>购买间隔时间下限_上限（毫秒）</t>
+  </si>
+  <si>
+    <t>单次购买分数万分比下限_上限</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -190,6 +199,15 @@
     <t>isOpen</t>
   </si>
   <si>
+    <t>robotHaveMax</t>
+  </si>
+  <si>
+    <t>robotTime</t>
+  </si>
+  <si>
+    <t>robotSinglePurchase</t>
+  </si>
+  <si>
     <t>Audi</t>
   </si>
   <si>
@@ -197,6 +215,12 @@
   </si>
   <si>
     <t>wdcc_ccb_3.png</t>
+  </si>
+  <si>
+    <t>10000_60000</t>
+  </si>
+  <si>
+    <t>500_1000</t>
   </si>
   <si>
     <t>Honda</t>
@@ -1213,7 +1237,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="7" style="3" customWidth="1"/>
@@ -1226,10 +1250,13 @@
     <col min="10" max="10" width="14.125" style="3" customWidth="1"/>
     <col min="11" max="11" width="23.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="10.625" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="3"/>
+    <col min="13" max="13" width="19.4166666666667" style="3" customWidth="1"/>
+    <col min="14" max="14" width="30.625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="28.5" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1266,81 +1293,108 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:15">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="N2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:15">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1357,7 +1411,7 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1366,7 +1420,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1378,7 +1432,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1">
         <v>5</v>
@@ -1387,13 +1441,22 @@
         <v>4320</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L5" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M5" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:12">
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1402,7 +1465,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1414,7 +1477,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I6" s="1">
         <v>5</v>
@@ -1423,13 +1486,22 @@
         <v>4320</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M6" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:12">
+    <row r="7" s="2" customFormat="1" spans="1:15">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1449,7 +1521,7 @@
         <v>200</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
@@ -1460,8 +1532,17 @@
       <c r="L7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M7" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:12">
+    <row r="8" s="2" customFormat="1" spans="1:15">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1481,7 +1562,7 @@
         <v>200</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1">
         <v>10</v>
@@ -1492,8 +1573,17 @@
       <c r="L8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M8" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:12">
+    <row r="9" s="2" customFormat="1" spans="1:15">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -1513,7 +1603,7 @@
         <v>300</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1">
         <v>10</v>
@@ -1524,8 +1614,17 @@
       <c r="L9" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M9" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:12">
+    <row r="10" s="2" customFormat="1" spans="1:15">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -1545,7 +1644,7 @@
         <v>300</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1">
         <v>10</v>
@@ -1556,8 +1655,17 @@
       <c r="L10" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="M10" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:12">
+    <row r="11" s="2" customFormat="1" spans="1:15">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -1577,7 +1685,7 @@
         <v>400</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I11" s="1">
         <v>20</v>
@@ -1588,8 +1696,17 @@
       <c r="L11" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="M11" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:12">
+    <row r="12" s="2" customFormat="1" spans="1:15">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -1609,7 +1726,7 @@
         <v>400</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I12" s="1">
         <v>20</v>
@@ -1620,8 +1737,17 @@
       <c r="L12" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="M12" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:12">
+    <row r="13" s="2" customFormat="1" spans="1:15">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -1641,7 +1767,7 @@
         <v>500</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1">
         <v>20</v>
@@ -1651,6 +1777,15 @@
       </c>
       <c r="L13" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4000</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1"/>

--- a/hall/resources/sample/MGLuckyTreasure.xlsx
+++ b/hall/resources/sample/MGLuckyTreasure.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="41">
   <si>
     <t>序列ID</t>
   </si>
@@ -1250,9 +1250,7 @@
     <col min="10" max="10" width="14.125" style="3" customWidth="1"/>
     <col min="11" max="11" width="23.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="10.625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="19.4166666666667" style="3" customWidth="1"/>
-    <col min="14" max="14" width="30.625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="28.5" style="3" customWidth="1"/>
+    <col min="13" max="15" width="12.25" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -1512,13 +1510,13 @@
         <v>1023001</v>
       </c>
       <c r="E7" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F7" s="1">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="G7" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>35</v>
@@ -1556,10 +1554,10 @@
         <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="G8" s="2">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>35</v>
@@ -1594,19 +1592,19 @@
         <v>1023201</v>
       </c>
       <c r="E9" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1">
-        <v>18000</v>
+        <v>14400</v>
       </c>
       <c r="G9" s="2">
-        <v>300</v>
+        <v>72</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J9" s="1">
         <v>4320</v>
@@ -1635,19 +1633,19 @@
         <v>1023301</v>
       </c>
       <c r="E10" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1">
-        <v>20000</v>
+        <v>16800</v>
       </c>
       <c r="G10" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J10" s="1">
         <v>4320</v>
@@ -1673,22 +1671,22 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>1023203</v>
+        <v>1023401</v>
       </c>
       <c r="E11" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
-        <v>22000</v>
+        <v>19200</v>
       </c>
       <c r="G11" s="2">
-        <v>400</v>
+        <v>96</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J11" s="1">
         <v>4320</v>
@@ -1714,22 +1712,22 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>1023303</v>
+        <v>1023002</v>
       </c>
       <c r="E12" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F12" s="1">
-        <v>24000</v>
+        <v>6000</v>
       </c>
       <c r="G12" s="2">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J12" s="1">
         <v>4320</v>
@@ -1755,22 +1753,22 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>1023403</v>
+        <v>1023102</v>
       </c>
       <c r="E13" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
-        <v>26000</v>
+        <v>9000</v>
       </c>
       <c r="G13" s="2">
-        <v>500</v>
+        <v>45</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1">
         <v>4320</v>
@@ -1788,9 +1786,129 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1"/>
-    <row r="15" s="2" customFormat="1"/>
-    <row r="16" s="2" customFormat="1"/>
+    <row r="14" s="2" customFormat="1" spans="1:15">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1023202</v>
+      </c>
+      <c r="E14" s="2">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2">
+        <v>18000</v>
+      </c>
+      <c r="G14" s="2">
+        <v>90</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="2">
+        <v>25</v>
+      </c>
+      <c r="J14" s="2">
+        <v>4320</v>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>4000</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:15">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1023302</v>
+      </c>
+      <c r="E15" s="2">
+        <v>35</v>
+      </c>
+      <c r="F15" s="2">
+        <v>25200</v>
+      </c>
+      <c r="G15" s="2">
+        <v>127</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="2">
+        <v>30</v>
+      </c>
+      <c r="J15" s="2">
+        <v>4320</v>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>4000</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:15">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1023402</v>
+      </c>
+      <c r="E16" s="2">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2">
+        <v>28800</v>
+      </c>
+      <c r="G16" s="2">
+        <v>145</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="2">
+        <v>35</v>
+      </c>
+      <c r="J16" s="2">
+        <v>4320</v>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>4000</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/hall/resources/sample/MGLuckyTreasure.xlsx
+++ b/hall/resources/sample/MGLuckyTreasure.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>序列ID</t>
   </si>
@@ -208,7 +208,7 @@
     <t>robotSinglePurchase</t>
   </si>
   <si>
-    <t>Audi</t>
+    <t>ipone8</t>
   </si>
   <si>
     <t>1022503_1</t>
@@ -221,12 +221,6 @@
   </si>
   <si>
     <t>500_1000</t>
-  </si>
-  <si>
-    <t>Honda</t>
-  </si>
-  <si>
-    <t>itemicon_1010201.png</t>
   </si>
 </sst>
 </file>
@@ -409,12 +403,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -876,7 +870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -896,6 +890,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1237,20 +1234,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="7" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12" style="3" customWidth="1"/>
-    <col min="5" max="6" width="9.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="7" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="3" customWidth="1"/>
     <col min="9" max="9" width="18.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="3" customWidth="1"/>
-    <col min="13" max="15" width="12.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="17.125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="21.25" style="3" customWidth="1"/>
+    <col min="14" max="14" width="30.625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="28.5" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -1291,13 +1292,13 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1341,10 +1342,10 @@
       <c r="M2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1385,17 +1386,17 @@
       <c r="L3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:15">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1408,6 +1409,9 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="1">
@@ -1454,25 +1458,24 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:15">
-      <c r="A6" s="1">
+    <row r="6" s="2" customFormat="1" spans="1:15">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
-        <v>39</v>
+      <c r="C6" s="2">
+        <v>1990000</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="F6" s="1">
-        <v>12000</v>
-      </c>
-      <c r="G6" s="1">
         <v>100</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>35</v>
@@ -1482,9 +1485,6 @@
       </c>
       <c r="J6" s="1">
         <v>4320</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="L6" s="1" t="b">
         <v>1</v>
@@ -1501,28 +1501,28 @@
     </row>
     <row r="7" s="2" customFormat="1" spans="1:15">
       <c r="A7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
       </c>
       <c r="C7" s="2">
-        <v>1023001</v>
+        <v>1980000</v>
       </c>
       <c r="E7" s="1">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="F7" s="1">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1">
         <v>4320</v>
@@ -1542,28 +1542,28 @@
     </row>
     <row r="8" s="2" customFormat="1" spans="1:15">
       <c r="A8" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="2">
-        <v>1023101</v>
+        <v>1202501</v>
       </c>
       <c r="E8" s="1">
         <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>6000</v>
+        <v>200</v>
       </c>
       <c r="G8" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J8" s="1">
         <v>4320</v>
@@ -1583,22 +1583,22 @@
     </row>
     <row r="9" s="2" customFormat="1" spans="1:15">
       <c r="A9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="2">
-        <v>1023201</v>
+        <v>1202502</v>
       </c>
       <c r="E9" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
-        <v>14400</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>35</v>
@@ -1622,293 +1622,45 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:15">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1023301</v>
-      </c>
-      <c r="E10" s="1">
-        <v>35</v>
-      </c>
-      <c r="F10" s="1">
-        <v>16800</v>
-      </c>
-      <c r="G10" s="2">
-        <v>84</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="1">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1">
-        <v>4320</v>
-      </c>
-      <c r="L10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
-        <v>4000</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="10" s="2" customFormat="1" spans="5:15">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:15">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1023401</v>
-      </c>
-      <c r="E11" s="1">
-        <v>20</v>
-      </c>
-      <c r="F11" s="1">
-        <v>19200</v>
-      </c>
-      <c r="G11" s="2">
-        <v>96</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="1">
-        <v>25</v>
-      </c>
-      <c r="J11" s="1">
-        <v>4320</v>
-      </c>
-      <c r="L11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>4000</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="11" s="2" customFormat="1" spans="5:15">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:15">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1023002</v>
-      </c>
-      <c r="E12" s="1">
-        <v>200</v>
-      </c>
-      <c r="F12" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G12" s="2">
-        <v>30</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="1">
-        <v>10</v>
-      </c>
-      <c r="J12" s="1">
-        <v>4320</v>
-      </c>
-      <c r="L12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>4000</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="12" s="2" customFormat="1" spans="5:15">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:15">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1023102</v>
-      </c>
-      <c r="E13" s="1">
-        <v>100</v>
-      </c>
-      <c r="F13" s="1">
-        <v>9000</v>
-      </c>
-      <c r="G13" s="2">
-        <v>45</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="1">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1">
-        <v>4320</v>
-      </c>
-      <c r="L13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>4000</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:15">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1023202</v>
-      </c>
-      <c r="E14" s="2">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2">
-        <v>18000</v>
-      </c>
-      <c r="G14" s="2">
-        <v>90</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="2">
-        <v>25</v>
-      </c>
-      <c r="J14" s="2">
-        <v>4320</v>
-      </c>
-      <c r="L14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2">
-        <v>4000</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:15">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1023302</v>
-      </c>
-      <c r="E15" s="2">
-        <v>35</v>
-      </c>
-      <c r="F15" s="2">
-        <v>25200</v>
-      </c>
-      <c r="G15" s="2">
-        <v>127</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="2">
-        <v>30</v>
-      </c>
-      <c r="J15" s="2">
-        <v>4320</v>
-      </c>
-      <c r="L15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2">
-        <v>4000</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:15">
-      <c r="A16" s="2">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
-        <v>2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1023402</v>
-      </c>
-      <c r="E16" s="2">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2">
-        <v>28800</v>
-      </c>
-      <c r="G16" s="2">
-        <v>145</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="2">
-        <v>35</v>
-      </c>
-      <c r="J16" s="2">
-        <v>4320</v>
-      </c>
-      <c r="L16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2">
-        <v>4000</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
+    <row r="13" s="2" customFormat="1"/>
+    <row r="14" s="2" customFormat="1"/>
+    <row r="15" s="2" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/hall/resources/sample/MGLuckyTreasure.xlsx
+++ b/hall/resources/sample/MGLuckyTreasure.xlsx
@@ -1469,10 +1469,10 @@
         <v>1990000</v>
       </c>
       <c r="E6" s="1">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="F6" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2">
         <v>10</v>
@@ -1622,7 +1622,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="5:15">
+    <row r="10" s="2" customFormat="1" spans="1:15">
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2"/>
@@ -1634,7 +1634,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="1" spans="5:15">
+    <row r="11" s="2" customFormat="1" spans="1:15">
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="2"/>
@@ -1646,7 +1646,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="5:15">
+    <row r="12" s="2" customFormat="1" spans="1:15">
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="2"/>
